--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260716.xlsx
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,447,296</t>
+          <t>183,515</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>183,515</t>
+          <t>5,447,296</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,317,520</t>
+          <t>1,343,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,343,000</t>
+          <t>5,317,520</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,234,000</t>
+          <t>5,742,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>811,897</t>
+          <t>3,234,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,839,000</t>
+          <t>811,897</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,742,000</t>
+          <t>1,839,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>772,000</t>
+          <t>940,659</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>940,659</t>
+          <t>772,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,470,578</t>
+          <t>584,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,384,384</t>
+          <t>4,470,578</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>584,000</t>
+          <t>1,384,384</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>779,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,198,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>779,000</t>
+          <t>2,198,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>1,189,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,189,076</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>4,978,956</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>4,978,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,566,400</t>
+          <t>807,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>807,000</t>
+          <t>1,566,400</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>321,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>157,000</t>
+          <t>171,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>321,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>157,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>1,764,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>255,000</t>
+          <t>682,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>682,000</t>
+          <t>332,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>255,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
